--- a/test-corpus/oracle/xlsx-synthetic-violations.xlsx
+++ b/test-corpus/oracle/xlsx-synthetic-violations.xlsx
@@ -134,6 +134,16 @@
 </table>
 </file>
 
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table1" displayName="Table1" ref="E1:F2" headerRowCount="1">
+  <autoFilter ref="E1:F2"/>
+  <tableColumns count="2">
+    <tableColumn id="5" name="Header1"/>
+    <tableColumn id="6" name="Header2"/>
+  </tableColumns>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -423,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +452,16 @@
           <t>R1C3</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Header1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Header2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -457,6 +477,16 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Data2</t>
         </is>
       </c>
     </row>
@@ -792,8 +822,9 @@
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>